--- a/orengeHRM/xldata/orengeHRMTestcases.xlsx
+++ b/orengeHRM/xldata/orengeHRMTestcases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7620" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="masterTestcases" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="104">
   <si>
     <t>Testcases id</t>
   </si>
@@ -59,15 +59,15 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>PIM</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>TC003</t>
-  </si>
-  <si>
-    <t>PIM</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -206,16 +206,16 @@
     <t>systemUser_userName</t>
   </si>
   <si>
-    <t>varafdfhdt</t>
-  </si>
-  <si>
-    <t>wait for systemuser</t>
+    <t>varafdfhdtlq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wait for Status </t>
   </si>
   <si>
     <t>systemUser[status]</t>
   </si>
   <si>
-    <t>select the systemuser</t>
+    <t xml:space="preserve">select the Status </t>
   </si>
   <si>
     <t>//*[@name='systemUser[password]']</t>
@@ -227,7 +227,7 @@
     <t>//input[@id='systemUser_confirmPassword']</t>
   </si>
   <si>
-    <t>wait foe sometime</t>
+    <t>wait for sometime</t>
   </si>
   <si>
     <t>ThreadsleepAction</t>
@@ -248,7 +248,7 @@
     <t>enter the username</t>
   </si>
   <si>
-    <t>uday123</t>
+    <t>varafdfhdt1</t>
   </si>
   <si>
     <t>click on search</t>
@@ -267,6 +267,81 @@
   </si>
   <si>
     <t>verifyusernametable</t>
+  </si>
+  <si>
+    <t>wait for PIM menu</t>
+  </si>
+  <si>
+    <t>//b[normalize-space()='PIM']</t>
+  </si>
+  <si>
+    <t>click on PIM</t>
+  </si>
+  <si>
+    <t>wait for add button</t>
+  </si>
+  <si>
+    <t>//input[@name='btnAdd']</t>
+  </si>
+  <si>
+    <t>enter the firstname</t>
+  </si>
+  <si>
+    <t>//input[@name='firstName']</t>
+  </si>
+  <si>
+    <t>uday</t>
+  </si>
+  <si>
+    <t>enter the midname</t>
+  </si>
+  <si>
+    <t>//input[@id='middleName']</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>enter the lastname</t>
+  </si>
+  <si>
+    <t>//input[@id='lastName']</t>
+  </si>
+  <si>
+    <t>varm</t>
+  </si>
+  <si>
+    <t>captureemployeid</t>
+  </si>
+  <si>
+    <t>employeeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wait for some time </t>
+  </si>
+  <si>
+    <t>//input[@id='photofile']</t>
+  </si>
+  <si>
+    <t>select the file location</t>
+  </si>
+  <si>
+    <t>UploadFile</t>
+  </si>
+  <si>
+    <t>C:/Users/DELL/Downloads/Hybridstructure_lyst1750226921116 (2).text</t>
+  </si>
+  <si>
+    <t>click the radiobutton</t>
+  </si>
+  <si>
+    <t>//input[@id='chkLogin']</t>
+  </si>
+  <si>
+    <t>click on save button</t>
+  </si>
+  <si>
+    <t>//input[@id='btnSave']</t>
   </si>
 </sst>
 </file>
@@ -279,7 +354,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,6 +369,12 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -640,7 +721,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -655,19 +736,6 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -794,16 +862,13 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -812,119 +877,122 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -937,10 +1005,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1526,19 +1597,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -1752,7 +1823,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="27.5714285714286" customWidth="1"/>
@@ -2017,10 +2088,10 @@
       <c r="F14" s="3"/>
     </row>
     <row r="15" customFormat="1" spans="1:6">
-      <c r="A15" t="s">
+      <c r="A15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -2038,7 +2109,7 @@
       <c r="A16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -2065,7 +2136,7 @@
       <c r="D17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="3"/>
@@ -2083,7 +2154,7 @@
       <c r="D18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>29</v>
       </c>
       <c r="F18" s="3"/>
@@ -2101,7 +2172,7 @@
       <c r="D19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="4">
         <v>3000</v>
       </c>
       <c r="F19" s="3"/>
@@ -2126,28 +2197,28 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="3">
-        <v>10</v>
+        <v>68</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>25</v>
@@ -2155,53 +2226,53 @@
       <c r="D22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>72</v>
+      <c r="E22" s="3">
+        <v>2000</v>
       </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>44</v>
@@ -2209,10 +2280,28 @@
       <c r="D25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>72</v>
+      <c r="E25" s="3">
+        <v>10</v>
       </c>
       <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2223,9 +2312,344 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="26.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="26.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="33.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="70.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="12.5714285714286" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="18.75" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="4">
+        <v>10</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="4">
+        <v>10</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/orengeHRM/xldata/orengeHRMTestcases.xlsx
+++ b/orengeHRM/xldata/orengeHRMTestcases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620" activeTab="3"/>
+    <workbookView windowWidth="20490" windowHeight="7620" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="masterTestcases" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="108">
   <si>
     <t>Testcases id</t>
   </si>
@@ -50,7 +50,7 @@
     <t>Applicationlogin</t>
   </si>
   <si>
-    <t>Y</t>
+    <t>N</t>
   </si>
   <si>
     <t>TC002</t>
@@ -59,13 +59,16 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>y</t>
+  </si>
+  <si>
     <t>TC003</t>
   </si>
   <si>
     <t>PIM</t>
   </si>
   <si>
-    <t>N</t>
+    <t>n</t>
   </si>
   <si>
     <t>Description</t>
@@ -206,13 +209,13 @@
     <t>systemUser_userName</t>
   </si>
   <si>
-    <t>varafdfhdtlq</t>
+    <t>vafhsddsf</t>
   </si>
   <si>
     <t xml:space="preserve">wait for Status </t>
   </si>
   <si>
-    <t>systemUser[status]</t>
+    <t>//select[@id='systemUser_status']</t>
   </si>
   <si>
     <t xml:space="preserve">select the Status </t>
@@ -239,16 +242,22 @@
     <t>btnSave</t>
   </si>
   <si>
+    <t>wait for save button</t>
+  </si>
+  <si>
+    <t>//input[@id='btnSave']</t>
+  </si>
+  <si>
     <t>wait for username searchbutton</t>
   </si>
   <si>
-    <t>searchSystemUser_userName</t>
+    <t>click on username</t>
   </si>
   <si>
     <t>enter the username</t>
   </si>
   <si>
-    <t>varafdfhdt1</t>
+    <t>//input[@id='searchSystemUser_userName']</t>
   </si>
   <si>
     <t>click on search</t>
@@ -329,19 +338,22 @@
     <t>UploadFile</t>
   </si>
   <si>
-    <t>C:/Users/DELL/Downloads/Hybridstructure_lyst1750226921116 (2).text</t>
-  </si>
-  <si>
-    <t>click the radiobutton</t>
-  </si>
-  <si>
-    <t>//input[@id='chkLogin']</t>
+    <t>C:/Users/DELL/Downloads/Hybridstructure_lyst1750226921116 (2).text'</t>
   </si>
   <si>
     <t>click on save button</t>
   </si>
   <si>
-    <t>//input[@id='btnSave']</t>
+    <t>wait for emplottable</t>
+  </si>
+  <si>
+    <t>verify the employid</t>
+  </si>
+  <si>
+    <t>employtable</t>
+  </si>
+  <si>
+    <t>//*[@id='resultTable']/tbody/tr[1]/td[2]/a</t>
   </si>
 </sst>
 </file>
@@ -992,7 +1004,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1005,13 +1017,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1597,19 +1609,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -1634,72 +1646,72 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18.75" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
@@ -1708,34 +1720,34 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="3">
         <v>3000</v>
@@ -1744,34 +1756,34 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3">
         <v>3000</v>
@@ -1780,37 +1792,37 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="3"/>
     </row>
@@ -1823,7 +1835,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="27.5714285714286" customWidth="1"/>
@@ -1835,72 +1847,72 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18.75" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
@@ -1909,70 +1921,70 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3">
         <v>10</v>
@@ -1981,52 +1993,52 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" customFormat="1" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3">
         <v>10</v>
@@ -2035,16 +2047,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -2053,52 +2065,52 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" customFormat="1" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>43</v>
+      <c r="A15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" s="3">
         <v>10</v>
@@ -2107,16 +2119,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
@@ -2125,127 +2137,127 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>29</v>
+        <v>63</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>29</v>
+        <v>65</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="4">
+        <v>21</v>
+      </c>
+      <c r="E19" s="3">
         <v>3000</v>
       </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>20</v>
+        <v>71</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3000</v>
       </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2000</v>
+      <c r="E22" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>72</v>
+        <v>58</v>
+      </c>
+      <c r="E23" s="3">
+        <v>10</v>
       </c>
       <c r="F23" s="3"/>
     </row>
@@ -2254,54 +2266,90 @@
         <v>73</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="3">
-        <v>10</v>
+      <c r="E25" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="3">
+        <v>10</v>
+      </c>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2312,7 +2360,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="26.4285714285714" customWidth="1"/>
@@ -2325,72 +2373,72 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18.75" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
@@ -2399,255 +2447,273 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="3">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="4">
-        <v>10</v>
-      </c>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="4">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" s="4">
-        <v>3000</v>
-      </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="4"/>
+      <c r="C17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="4"/>
+      <c r="A18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/orengeHRM/xldata/orengeHRMTestcases.xlsx
+++ b/orengeHRM/xldata/orengeHRMTestcases.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620" activeTab="2"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="masterTestcases" sheetId="1" r:id="rId1"/>
     <sheet name="Applicationlogin" sheetId="2" r:id="rId2"/>
     <sheet name="Admin" sheetId="3" r:id="rId3"/>
     <sheet name="PIM" sheetId="4" r:id="rId4"/>
+    <sheet name="Recruitment" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="130">
   <si>
     <t>Testcases id</t>
   </si>
@@ -59,18 +60,21 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>PIM</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>Recruitment</t>
+  </si>
+  <si>
     <t>y</t>
   </si>
   <si>
-    <t>TC003</t>
-  </si>
-  <si>
-    <t>PIM</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -209,7 +213,7 @@
     <t>systemUser_userName</t>
   </si>
   <si>
-    <t>vafhsddsf</t>
+    <t>uday121l</t>
   </si>
   <si>
     <t xml:space="preserve">wait for Status </t>
@@ -239,45 +243,36 @@
     <t>click on the savebutton</t>
   </si>
   <si>
-    <t>btnSave</t>
+    <t>//input[@id='btnSave']</t>
   </si>
   <si>
     <t>wait for save button</t>
   </si>
   <si>
-    <t>//input[@id='btnSave']</t>
-  </si>
-  <si>
-    <t>wait for username searchbutton</t>
-  </si>
-  <si>
-    <t>click on username</t>
+    <t>wait for the username</t>
+  </si>
+  <si>
+    <t>//input[@name='searchSystemUser[userName]']</t>
   </si>
   <si>
     <t>enter the username</t>
   </si>
   <si>
-    <t>//input[@id='searchSystemUser_userName']</t>
-  </si>
-  <si>
-    <t>click on search</t>
+    <t>click on the search button</t>
   </si>
   <si>
     <t>//input[@id='searchBtn']</t>
   </si>
   <si>
-    <t>wait for usernamein table</t>
+    <t>verify the usernamein table</t>
+  </si>
+  <si>
+    <t>verifyusernametable</t>
   </si>
   <si>
     <t>//table[@id='resultTable']/tbody/tr[1]/td[2]</t>
   </si>
   <si>
-    <t>verify the usernamein table</t>
-  </si>
-  <si>
-    <t>verifyusernametable</t>
-  </si>
-  <si>
     <t>wait for PIM menu</t>
   </si>
   <si>
@@ -332,15 +327,6 @@
     <t>//input[@id='photofile']</t>
   </si>
   <si>
-    <t>select the file location</t>
-  </si>
-  <si>
-    <t>UploadFile</t>
-  </si>
-  <si>
-    <t>C:/Users/DELL/Downloads/Hybridstructure_lyst1750226921116 (2).text'</t>
-  </si>
-  <si>
     <t>click on save button</t>
   </si>
   <si>
@@ -354,6 +340,87 @@
   </si>
   <si>
     <t>//*[@id='resultTable']/tbody/tr[1]/td[2]/a</t>
+  </si>
+  <si>
+    <t>wait for Recruitment</t>
+  </si>
+  <si>
+    <t>//b[normalize-space()='Recruitment']</t>
+  </si>
+  <si>
+    <t>clikck on the recruitment</t>
+  </si>
+  <si>
+    <t>//input[@id='btnAdd']</t>
+  </si>
+  <si>
+    <t>wait for firstname</t>
+  </si>
+  <si>
+    <t>//input[@id='addCandidate_firstName']</t>
+  </si>
+  <si>
+    <t>//input[@id='addCandidate_middleName']</t>
+  </si>
+  <si>
+    <t>//input[@id='addCandidate_lastName']</t>
+  </si>
+  <si>
+    <t>varaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wait for email id </t>
+  </si>
+  <si>
+    <t>//input[@id='addCandidate_email']</t>
+  </si>
+  <si>
+    <t>enter the emailid</t>
+  </si>
+  <si>
+    <t>ydaa@gmail.com</t>
+  </si>
+  <si>
+    <t>wait for  contact</t>
+  </si>
+  <si>
+    <t>//input[@id='addCandidate_contactNo']</t>
+  </si>
+  <si>
+    <t>enter the contact number</t>
+  </si>
+  <si>
+    <t>enter the keypad</t>
+  </si>
+  <si>
+    <t>//input[@id='addCandidate_keyWords']</t>
+  </si>
+  <si>
+    <t>udaa</t>
+  </si>
+  <si>
+    <t>enter the comments</t>
+  </si>
+  <si>
+    <t>//textarea[@id='addCandidate_comment']</t>
+  </si>
+  <si>
+    <t>its working fine</t>
+  </si>
+  <si>
+    <t>select the datacalander</t>
+  </si>
+  <si>
+    <t>selectcalander</t>
+  </si>
+  <si>
+    <t>//input[@id='addCandidate_appliedDate']</t>
+  </si>
+  <si>
+    <t xml:space="preserve">click on checkbox </t>
+  </si>
+  <si>
+    <t>//input[@id='addCandidate_consentToKeepData']</t>
   </si>
 </sst>
 </file>
@@ -383,6 +450,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF1F1F1F"/>
       <name val="Courier New"/>
@@ -392,14 +467,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -874,12 +941,12 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1004,7 +1071,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1017,13 +1084,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1566,8 +1633,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="28.8571428571429" customWidth="1"/>
@@ -1609,21 +1676,33 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1646,72 +1725,72 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18.75" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
@@ -1720,34 +1799,34 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3">
         <v>3000</v>
@@ -1756,34 +1835,34 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="3">
         <v>3000</v>
@@ -1792,37 +1871,37 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="3"/>
     </row>
@@ -1847,72 +1926,72 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18.75" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
@@ -1921,70 +2000,70 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3">
         <v>10</v>
@@ -1993,52 +2072,52 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" customFormat="1" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3">
         <v>10</v>
@@ -2047,16 +2126,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -2065,52 +2144,52 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" customFormat="1" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="3">
         <v>10</v>
@@ -2119,16 +2198,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
@@ -2137,52 +2216,52 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>30</v>
+        <v>64</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>30</v>
+        <v>66</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" s="3">
         <v>3000</v>
@@ -2191,91 +2270,91 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="E21" s="3">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="3">
-        <v>10</v>
+        <v>70</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>21</v>
+      <c r="E24" s="3">
+        <v>20</v>
       </c>
       <c r="F24" s="3"/>
     </row>
@@ -2284,70 +2363,70 @@
         <v>74</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="3">
-        <v>10</v>
+      <c r="E27" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F28" s="3"/>
     </row>
@@ -2360,85 +2439,85 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="26.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="26.2857142857143" customWidth="1"/>
     <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="33.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="42.4285714285714" customWidth="1"/>
     <col min="5" max="5" width="70.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="12.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18.75" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
@@ -2447,52 +2526,52 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E7" s="3">
         <v>10</v>
@@ -2501,34 +2580,34 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3">
         <v>10</v>
@@ -2537,106 +2616,106 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>97</v>
+        <v>27</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E15" s="3">
         <v>5000</v>
@@ -2645,78 +2724,554 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>102</v>
+        <v>70</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="26.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="32.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="50.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="21.7142857142857" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="18.75" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20">
+        <v>9876576576</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E18" r:id="rId1" display="ydaa@gmail.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>